--- a/applicants.xlsx
+++ b/applicants.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kperc\Documents\2025-2026 (4A, Coop, 4B)\4B (Winter 2026)\MSE 402 - Capstone\capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicol\Documents\Shiftly\capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6BCE46-CAAB-4E1B-9242-F34582B84E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6985F5-FECF-4DED-A183-FD93C2D3445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C5DDFE8C-B9A4-4142-8A15-6BAE3ACCC87A}"/>
   </bookViews>
   <sheets>
-    <sheet name="kate_applicants" sheetId="1" r:id="rId1"/>
+    <sheet name="applicants" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -5002,7 +5002,7 @@
         <v>63</v>
       </c>
       <c r="N57" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O57" t="s">
         <v>28</v>
@@ -7511,7 +7511,7 @@
         <v>184</v>
       </c>
       <c r="C98" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
         <v>20</v>
@@ -7573,7 +7573,7 @@
         <v>187</v>
       </c>
       <c r="C99" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="D99" t="s">
         <v>20</v>
@@ -7635,7 +7635,7 @@
         <v>189</v>
       </c>
       <c r="C100" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
         <v>20</v>
@@ -7697,7 +7697,7 @@
         <v>191</v>
       </c>
       <c r="C101" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
         <v>20</v>
@@ -7759,7 +7759,7 @@
         <v>193</v>
       </c>
       <c r="C102" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="D102" t="s">
         <v>20</v>
@@ -7821,7 +7821,7 @@
         <v>195</v>
       </c>
       <c r="C103" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="D103" t="s">
         <v>20</v>
@@ -7883,7 +7883,7 @@
         <v>197</v>
       </c>
       <c r="C104" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="D104" t="s">
         <v>20</v>
@@ -7945,7 +7945,7 @@
         <v>199</v>
       </c>
       <c r="C105" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="D105" t="s">
         <v>20</v>
